--- a/IAI/XSEL_01/RB1_XSELティーチングポイント.xlsx
+++ b/IAI/XSEL_01/RB1_XSELティーチングポイント.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29530"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://isyswarekato-my.sharepoint.com/personal/m_miyashita_isyswarekato_onmicrosoft_com/Documents/DATA/テクノ/泰成_TE251202013_支持脚後部自動組立専用機/TA052_ボルト・キャップ組立機/SEL/RB1_箱詰め/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="38" documentId="13_ncr:1_{185007B6-462F-4BC4-AE35-6DA1F440DEF8}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{3270D66A-1CAF-4E2E-93F0-44B165F1BFF9}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{10120443-419E-418E-AF8C-90997F0530B9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-2070" yWindow="-18480" windowWidth="34755" windowHeight="18180" xr2:uid="{D43ABD46-B114-4A62-8646-7187B96B4F1A}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{D43ABD46-B114-4A62-8646-7187B96B4F1A}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="37">
   <si>
     <t>Pos.</t>
     <phoneticPr fontId="1"/>
@@ -65,22 +65,6 @@
     <phoneticPr fontId="1"/>
   </si>
   <si>
-    <t>箱詰め下降位置[Z軸]</t>
-    <rPh sb="0" eb="2">
-      <t>ハコツ</t>
-    </rPh>
-    <rPh sb="3" eb="5">
-      <t>カコウ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>イチ</t>
-    </rPh>
-    <rPh sb="9" eb="10">
-      <t>ジク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
     <t>RB1_箱詰めRBポジション</t>
     <rPh sb="4" eb="6">
       <t>ハコツ</t>
@@ -115,58 +99,6 @@
       <t>イチ</t>
     </rPh>
     <rPh sb="8" eb="9">
-      <t>ジク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>箱詰めP1位置[XY軸]</t>
-    <rPh sb="0" eb="2">
-      <t>ハコツ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>イチ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ジク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>箱詰めP2位置[XY軸]</t>
-    <rPh sb="0" eb="2">
-      <t>ハコツ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>イチ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ジク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>箱詰めP3位置[XY軸]</t>
-    <rPh sb="0" eb="2">
-      <t>ハコツ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>イチ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
-      <t>ジク</t>
-    </rPh>
-    <phoneticPr fontId="1"/>
-  </si>
-  <si>
-    <t>箱詰めP4位置[XY軸]</t>
-    <rPh sb="0" eb="2">
-      <t>ハコツ</t>
-    </rPh>
-    <rPh sb="5" eb="7">
-      <t>イチ</t>
-    </rPh>
-    <rPh sb="10" eb="11">
       <t>ジク</t>
     </rPh>
     <phoneticPr fontId="1"/>
@@ -227,6 +159,482 @@
     </rPh>
     <rPh sb="16" eb="18">
       <t>キンシ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未確定</t>
+    <rPh sb="0" eb="3">
+      <t>ミカクテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>箱:大 箱詰めP1位置[XY軸]</t>
+    <rPh sb="0" eb="1">
+      <t>ハコ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハコツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ジク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>箱:大 箱詰めP2位置[XY軸]</t>
+    <rPh sb="0" eb="1">
+      <t>ハコ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハコツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ジク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>箱:大 箱詰めP3位置[XY軸]</t>
+    <rPh sb="0" eb="1">
+      <t>ハコ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハコツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ジク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>箱:大 箱詰めP4位置[XY軸]</t>
+    <rPh sb="0" eb="1">
+      <t>ハコ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハコツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ジク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>箱:大 箱詰めP5位置[XY軸]</t>
+    <rPh sb="0" eb="1">
+      <t>ハコ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハコツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ジク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>箱:大 箱詰めP6位置[XY軸]</t>
+    <rPh sb="0" eb="1">
+      <t>ハコ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハコツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ジク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>箱:大 箱詰めP7位置[XY軸]</t>
+    <rPh sb="0" eb="1">
+      <t>ハコ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハコツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ジク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>箱:大 箱詰めP8位置[XY軸]</t>
+    <rPh sb="0" eb="1">
+      <t>ハコ</t>
+    </rPh>
+    <rPh sb="2" eb="3">
+      <t>ダイ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハコツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ジク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>未設定</t>
+    <rPh sb="0" eb="3">
+      <t>ミセッテイ</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>箱:小 箱詰めP1位置[XY軸]</t>
+    <rPh sb="0" eb="1">
+      <t>ハコ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハコツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ジク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>箱:小 箱詰めP2位置[XY軸]</t>
+    <rPh sb="0" eb="1">
+      <t>ハコ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハコツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ジク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>箱:小 箱詰めP3位置[XY軸]</t>
+    <rPh sb="0" eb="1">
+      <t>ハコ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハコツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ジク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>箱:小 箱詰めP4位置[XY軸]</t>
+    <rPh sb="0" eb="1">
+      <t>ハコ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハコツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ジク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>箱:小 箱詰めP5位置[XY軸]</t>
+    <rPh sb="0" eb="1">
+      <t>ハコ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハコツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ジク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>箱:小 箱詰めP6位置[XY軸]</t>
+    <rPh sb="0" eb="1">
+      <t>ハコ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハコツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ジク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>箱:小 箱詰めP7位置[XY軸]</t>
+    <rPh sb="0" eb="1">
+      <t>ハコ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハコツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ジク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>箱:小 箱詰めP8位置[XY軸]</t>
+    <rPh sb="0" eb="1">
+      <t>ハコ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハコツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ジク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>箱:中 箱詰めP1位置[XY軸]</t>
+    <rPh sb="0" eb="1">
+      <t>ハコ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハコツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ジク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>箱:中 箱詰めP2位置[XY軸]</t>
+    <rPh sb="0" eb="1">
+      <t>ハコ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハコツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ジク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>箱:中 箱詰めP3位置[XY軸]</t>
+    <rPh sb="0" eb="1">
+      <t>ハコ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハコツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ジク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>箱:中 箱詰めP4位置[XY軸]</t>
+    <rPh sb="0" eb="1">
+      <t>ハコ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハコツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ジク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>箱:中 箱詰めP5位置[XY軸]</t>
+    <rPh sb="0" eb="1">
+      <t>ハコ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハコツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ジク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>箱:中 箱詰めP6位置[XY軸]</t>
+    <rPh sb="0" eb="1">
+      <t>ハコ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハコツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ジク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>箱:中 箱詰めP7位置[XY軸]</t>
+    <rPh sb="0" eb="1">
+      <t>ハコ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハコツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ジク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>箱:中 箱詰めP8位置[XY軸]</t>
+    <rPh sb="0" eb="1">
+      <t>ハコ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハコツ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="14" eb="15">
+      <t>ジク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>箱:大 箱詰め下降位置[Z軸]</t>
+    <rPh sb="4" eb="6">
+      <t>ハコツ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カコウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ジク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>箱:小 箱詰め下降位置[Z軸]</t>
+    <rPh sb="2" eb="3">
+      <t>ショウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハコツ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カコウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ジク</t>
+    </rPh>
+    <phoneticPr fontId="1"/>
+  </si>
+  <si>
+    <t>箱:中 箱詰め下降位置[Z軸]</t>
+    <rPh sb="2" eb="3">
+      <t>チュウ</t>
+    </rPh>
+    <rPh sb="4" eb="6">
+      <t>ハコツ</t>
+    </rPh>
+    <rPh sb="7" eb="9">
+      <t>カコウ</t>
+    </rPh>
+    <rPh sb="9" eb="11">
+      <t>イチ</t>
+    </rPh>
+    <rPh sb="13" eb="14">
+      <t>ジク</t>
     </rPh>
     <phoneticPr fontId="1"/>
   </si>
@@ -311,10 +719,6 @@
     </ext>
   </extLst>
 </styleSheet>
-</file>
-
-<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
-<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -634,18 +1038,18 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{51DE2EAE-4B08-4412-BB5C-F19FABB7E51A}">
-  <dimension ref="A1:B37"/>
+  <dimension ref="A1:C47"/>
   <sheetFormatPr defaultRowHeight="18.75" x14ac:dyDescent="0.4"/>
   <cols>
     <col min="2" max="2" width="43.375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.4">
       <c r="B1" t="s">
-        <v>4</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.4">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A2" s="2" t="s">
         <v>0</v>
       </c>
@@ -653,7 +1057,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A3" s="2">
         <v>1</v>
       </c>
@@ -661,201 +1065,362 @@
         <v>2</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A4" s="2">
         <v>2</v>
       </c>
       <c r="B4" s="1" t="s">
-        <v>6</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.4">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A5" s="2">
         <v>3</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>3</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.4">
+        <v>34</v>
+      </c>
+    </row>
+    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A6" s="2">
         <v>4</v>
       </c>
-      <c r="B6" s="1"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B6" s="1" t="s">
+        <v>35</v>
+      </c>
+      <c r="C6" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A7" s="2">
         <v>5</v>
       </c>
-      <c r="B7" s="1"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B7" s="1" t="s">
+        <v>36</v>
+      </c>
+      <c r="C7" t="s">
+        <v>8</v>
+      </c>
+    </row>
+    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A8" s="2">
         <v>6</v>
       </c>
       <c r="B8" s="1"/>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A9" s="2">
         <v>7</v>
       </c>
       <c r="B9" s="1"/>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A10" s="2">
         <v>8</v>
       </c>
       <c r="B10" s="1"/>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A11" s="2">
         <v>9</v>
       </c>
       <c r="B11" s="1"/>
     </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A12" s="2">
         <v>10</v>
       </c>
       <c r="B12" s="1"/>
     </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A13" s="2">
         <v>11</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.4">
+        <v>4</v>
+      </c>
+    </row>
+    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A14" s="2">
         <v>12</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>7</v>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.4">
+        <v>9</v>
+      </c>
+    </row>
+    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A15" s="2">
         <v>13</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>8</v>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.4">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A16" s="2">
         <v>14</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="17" spans="1:2" x14ac:dyDescent="0.4">
+        <v>11</v>
+      </c>
+    </row>
+    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A17" s="2">
         <v>15</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="18" spans="1:2" x14ac:dyDescent="0.4">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A18" s="2">
         <v>16</v>
       </c>
-      <c r="B18" s="1"/>
-    </row>
-    <row r="19" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B18" s="1" t="s">
+        <v>13</v>
+      </c>
+      <c r="C18" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A19" s="2">
         <v>17</v>
       </c>
-      <c r="B19" s="1"/>
-    </row>
-    <row r="20" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B19" s="1" t="s">
+        <v>14</v>
+      </c>
+      <c r="C19" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A20" s="2">
         <v>18</v>
       </c>
-      <c r="B20" s="1"/>
-    </row>
-    <row r="21" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B20" s="1" t="s">
+        <v>15</v>
+      </c>
+      <c r="C20" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A21" s="2">
         <v>19</v>
       </c>
-      <c r="B21" s="1"/>
-    </row>
-    <row r="22" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B21" s="1" t="s">
+        <v>16</v>
+      </c>
+      <c r="C21" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A22" s="2">
         <v>20</v>
       </c>
       <c r="B22" s="1"/>
     </row>
-    <row r="23" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A23" s="2">
         <v>21</v>
       </c>
     </row>
-    <row r="24" spans="1:2" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A24" s="2">
         <v>22</v>
       </c>
-    </row>
-    <row r="25" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B24" s="1" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A25" s="2">
         <v>23</v>
       </c>
-    </row>
-    <row r="26" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B25" s="1" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A26" s="2">
         <v>24</v>
       </c>
-    </row>
-    <row r="27" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B26" s="1" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A27" s="2">
         <v>25</v>
       </c>
-      <c r="B27" s="1"/>
-    </row>
-    <row r="28" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B27" s="1" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A28" s="2">
         <v>26</v>
       </c>
-      <c r="B28" s="1"/>
-    </row>
-    <row r="29" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B28" s="1" t="s">
+        <v>22</v>
+      </c>
+      <c r="C28" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A29" s="2">
         <v>27</v>
       </c>
-      <c r="B29" s="1"/>
-    </row>
-    <row r="30" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B29" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="C29" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A30" s="2">
         <v>28</v>
       </c>
-    </row>
-    <row r="31" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B30" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="C30" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A31" s="2">
         <v>29</v>
       </c>
-    </row>
-    <row r="32" spans="1:2" x14ac:dyDescent="0.4">
+      <c r="B31" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C31" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
       <c r="A32" s="2">
         <v>30</v>
       </c>
     </row>
-    <row r="35" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A35" s="3">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A33" s="2">
+        <v>31</v>
+      </c>
+    </row>
+    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A34" s="2">
+        <v>32</v>
+      </c>
+      <c r="B34" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="C34" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="35" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A35" s="2">
+        <v>33</v>
+      </c>
+      <c r="B35" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="C35" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="36" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A36" s="2">
+        <v>34</v>
+      </c>
+      <c r="B36" s="1" t="s">
+        <v>28</v>
+      </c>
+      <c r="C36" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="37" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A37" s="2">
+        <v>35</v>
+      </c>
+      <c r="B37" s="1" t="s">
+        <v>29</v>
+      </c>
+      <c r="C37" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="38" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A38" s="2">
+        <v>36</v>
+      </c>
+      <c r="B38" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="C38" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="39" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A39" s="2">
+        <v>37</v>
+      </c>
+      <c r="B39" s="1" t="s">
+        <v>31</v>
+      </c>
+      <c r="C39" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="40" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A40" s="2">
+        <v>38</v>
+      </c>
+      <c r="B40" s="1" t="s">
+        <v>32</v>
+      </c>
+      <c r="C40" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="41" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A41" s="2">
+        <v>39</v>
+      </c>
+      <c r="B41" s="1" t="s">
+        <v>33</v>
+      </c>
+      <c r="C41" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="42" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A42" s="2">
+        <v>40</v>
+      </c>
+    </row>
+    <row r="45" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A45" s="3">
         <v>70</v>
       </c>
-      <c r="B35" s="4" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="37" spans="1:2" x14ac:dyDescent="0.4">
-      <c r="A37" s="3">
+      <c r="B45" s="4" t="s">
+        <v>7</v>
+      </c>
+    </row>
+    <row r="47" spans="1:3" x14ac:dyDescent="0.4">
+      <c r="A47" s="3">
         <v>80</v>
       </c>
-      <c r="B37" s="4" t="s">
-        <v>11</v>
+      <c r="B47" s="4" t="s">
+        <v>6</v>
       </c>
     </row>
   </sheetData>
